--- a/data/nzd0504/nzd0504.xlsx
+++ b/data/nzd0504/nzd0504.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J356"/>
+  <dimension ref="A1:J359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13256,6 +13256,114 @@
         <v>371.79</v>
       </c>
       <c r="J356" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>357.4</v>
+      </c>
+      <c r="C357" t="n">
+        <v>359.31</v>
+      </c>
+      <c r="D357" t="n">
+        <v>364.47</v>
+      </c>
+      <c r="E357" t="n">
+        <v>364.97</v>
+      </c>
+      <c r="F357" t="n">
+        <v>363.43</v>
+      </c>
+      <c r="G357" t="n">
+        <v>366.16</v>
+      </c>
+      <c r="H357" t="n">
+        <v>367.34</v>
+      </c>
+      <c r="I357" t="n">
+        <v>371.89</v>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>357.37</v>
+      </c>
+      <c r="C358" t="n">
+        <v>359.56</v>
+      </c>
+      <c r="D358" t="n">
+        <v>365.21</v>
+      </c>
+      <c r="E358" t="n">
+        <v>366.06</v>
+      </c>
+      <c r="F358" t="n">
+        <v>364.64</v>
+      </c>
+      <c r="G358" t="n">
+        <v>366.83</v>
+      </c>
+      <c r="H358" t="n">
+        <v>368.12</v>
+      </c>
+      <c r="I358" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>355.99</v>
+      </c>
+      <c r="C359" t="n">
+        <v>358.5</v>
+      </c>
+      <c r="D359" t="n">
+        <v>364.02</v>
+      </c>
+      <c r="E359" t="n">
+        <v>365.43</v>
+      </c>
+      <c r="F359" t="n">
+        <v>363.92</v>
+      </c>
+      <c r="G359" t="n">
+        <v>365.74</v>
+      </c>
+      <c r="H359" t="n">
+        <v>366.79</v>
+      </c>
+      <c r="I359" t="n">
+        <v>369.79</v>
+      </c>
+      <c r="J359" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13272,7 +13380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B408"/>
+  <dimension ref="A1:B411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17355,6 +17463,36 @@
       </c>
       <c r="B408" t="n">
         <v>-0.74</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
@@ -17523,28 +17661,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.651719467436276</v>
+        <v>0.6550618613503808</v>
       </c>
       <c r="J2" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K2" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2162025117850204</v>
+        <v>0.2206637569075109</v>
       </c>
       <c r="M2" t="n">
-        <v>6.862370317947766</v>
+        <v>6.822123813813132</v>
       </c>
       <c r="N2" t="n">
-        <v>73.97366658104477</v>
+        <v>73.39035193321111</v>
       </c>
       <c r="O2" t="n">
-        <v>8.600794531963007</v>
+        <v>8.566816907884229</v>
       </c>
       <c r="P2" t="n">
-        <v>337.4068168584765</v>
+        <v>337.3660623503346</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17601,28 +17739,28 @@
         <v>0.1167</v>
       </c>
       <c r="I3" t="n">
-        <v>0.677920319605587</v>
+        <v>0.6817450919251343</v>
       </c>
       <c r="J3" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K3" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2955592078700208</v>
+        <v>0.30116352202771</v>
       </c>
       <c r="M3" t="n">
-        <v>5.640804428485561</v>
+        <v>5.610946987535347</v>
       </c>
       <c r="N3" t="n">
-        <v>52.70770440783566</v>
+        <v>52.3095996876007</v>
       </c>
       <c r="O3" t="n">
-        <v>7.26000719061873</v>
+        <v>7.232537569041774</v>
       </c>
       <c r="P3" t="n">
-        <v>338.6207463337677</v>
+        <v>338.5741092684518</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17679,28 +17817,28 @@
         <v>0.1314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6727096752472556</v>
+        <v>0.676415845861737</v>
       </c>
       <c r="J4" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K4" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3098637892276638</v>
+        <v>0.3155608886934853</v>
       </c>
       <c r="M4" t="n">
-        <v>5.405218704688711</v>
+        <v>5.380647664112617</v>
       </c>
       <c r="N4" t="n">
-        <v>48.42080004339201</v>
+        <v>48.05733338802796</v>
       </c>
       <c r="O4" t="n">
-        <v>6.958505589808204</v>
+        <v>6.932339676330638</v>
       </c>
       <c r="P4" t="n">
-        <v>344.2746209394405</v>
+        <v>344.2294197186504</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17757,28 +17895,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6221724592435361</v>
+        <v>0.6238276015506083</v>
       </c>
       <c r="J5" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K5" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2850260513301546</v>
+        <v>0.2894288161797336</v>
       </c>
       <c r="M5" t="n">
-        <v>5.166242345568622</v>
+        <v>5.132216010173344</v>
       </c>
       <c r="N5" t="n">
-        <v>46.64873302146206</v>
+        <v>46.26744003183418</v>
       </c>
       <c r="O5" t="n">
-        <v>6.82998777608438</v>
+        <v>6.802017350156803</v>
       </c>
       <c r="P5" t="n">
-        <v>347.7810193216434</v>
+        <v>347.7608259522531</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17835,28 +17973,28 @@
         <v>0.0824</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6118450595708655</v>
+        <v>0.6132913185051855</v>
       </c>
       <c r="J6" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K6" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2613454041346093</v>
+        <v>0.2654120261912464</v>
       </c>
       <c r="M6" t="n">
-        <v>5.437914500367121</v>
+        <v>5.399961240924638</v>
       </c>
       <c r="N6" t="n">
-        <v>50.83023033220705</v>
+        <v>50.41239442952487</v>
       </c>
       <c r="O6" t="n">
-        <v>7.129532266019073</v>
+        <v>7.100168619795228</v>
       </c>
       <c r="P6" t="n">
-        <v>346.6949972188219</v>
+        <v>346.6773510409131</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17913,28 +18051,28 @@
         <v>0.094</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6069848342084057</v>
+        <v>0.6085464039338787</v>
       </c>
       <c r="J7" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K7" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2624791577375072</v>
+        <v>0.2666348032927591</v>
       </c>
       <c r="M7" t="n">
-        <v>5.28951887766345</v>
+        <v>5.253065155644055</v>
       </c>
       <c r="N7" t="n">
-        <v>49.73335754659372</v>
+        <v>49.32548169634843</v>
       </c>
       <c r="O7" t="n">
-        <v>7.052188138910768</v>
+        <v>7.023210213025695</v>
       </c>
       <c r="P7" t="n">
-        <v>349.0008978249277</v>
+        <v>348.9818540113869</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17991,28 +18129,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6478921087298271</v>
+        <v>0.6465242506856033</v>
       </c>
       <c r="J8" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K8" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L8" t="n">
-        <v>0.298785366095064</v>
+        <v>0.3013061587286172</v>
       </c>
       <c r="M8" t="n">
-        <v>5.198034196477219</v>
+        <v>5.160453384099584</v>
       </c>
       <c r="N8" t="n">
-        <v>47.32707390721863</v>
+        <v>46.93847984833941</v>
       </c>
       <c r="O8" t="n">
-        <v>6.879467559863818</v>
+        <v>6.851166312996599</v>
       </c>
       <c r="P8" t="n">
-        <v>350.829791760894</v>
+        <v>350.8464788054206</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18069,28 +18207,28 @@
         <v>0.0586</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4961683699003329</v>
+        <v>0.4948947229071113</v>
       </c>
       <c r="J9" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K9" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1657574197069828</v>
+        <v>0.1672931784480782</v>
       </c>
       <c r="M9" t="n">
-        <v>5.657790417169229</v>
+        <v>5.617282179551682</v>
       </c>
       <c r="N9" t="n">
-        <v>59.52373173696976</v>
+        <v>59.03641957051188</v>
       </c>
       <c r="O9" t="n">
-        <v>7.715162456939566</v>
+        <v>7.683516094244346</v>
       </c>
       <c r="P9" t="n">
-        <v>358.42547416628</v>
+        <v>358.4410281015681</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18128,7 +18266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J356"/>
+  <dimension ref="A1:J359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36639,6 +36777,162 @@
         </is>
       </c>
     </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-45.800004091185386,170.74150290535138</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-45.800582793035666,170.7418373086107</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-45.80113660088658,170.74223479807293</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-45.801680001225584,170.7426164836575</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-45.80220483453375,170.74307029974284</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-45.80271986265595,170.74357822979647</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-45.803228802665096,170.7440766789811</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-45.80369953741844,170.7446568498229</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-45.8000041800578,170.74150254096872</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>-45.80058201753678,170.7418403273056</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>-45.80113402387565,170.74224357518997</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-45.801675430490945,170.74262888913947</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-45.802199208342735,170.74308362530547</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-45.802716700773,170.74358556789133</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-45.80322488557075,170.7440850045187</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-45.803702635257224,170.74465068638634</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-45.80000826818766,170.74148577936438</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>-45.8005853056515,170.74182752803875</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-45.80113816798749,170.74222946063654</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-45.80167807229187,170.74262171899875</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-45.802202556159074,170.74307569604537</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-45.802721844731565,170.7435736297963</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-45.803231564718416,170.74407080840905</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-45.80371056362274,170.74463491216423</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0504/nzd0504.xlsx
+++ b/data/nzd0504/nzd0504.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J359"/>
+  <dimension ref="A1:J361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13364,6 +13364,78 @@
         <v>369.79</v>
       </c>
       <c r="J359" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:14:11+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>354.92</v>
+      </c>
+      <c r="C360" t="n">
+        <v>358.04</v>
+      </c>
+      <c r="D360" t="n">
+        <v>363.68</v>
+      </c>
+      <c r="E360" t="n">
+        <v>365.26</v>
+      </c>
+      <c r="F360" t="n">
+        <v>363.66</v>
+      </c>
+      <c r="G360" t="n">
+        <v>365.34</v>
+      </c>
+      <c r="H360" t="n">
+        <v>365.44</v>
+      </c>
+      <c r="I360" t="n">
+        <v>368.07</v>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>354.47</v>
+      </c>
+      <c r="C361" t="n">
+        <v>358.1</v>
+      </c>
+      <c r="D361" t="n">
+        <v>363.52</v>
+      </c>
+      <c r="E361" t="n">
+        <v>365.36</v>
+      </c>
+      <c r="F361" t="n">
+        <v>363.47</v>
+      </c>
+      <c r="G361" t="n">
+        <v>365.16</v>
+      </c>
+      <c r="H361" t="n">
+        <v>365.57</v>
+      </c>
+      <c r="I361" t="n">
+        <v>367.27</v>
+      </c>
+      <c r="J361" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13380,7 +13452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B411"/>
+  <dimension ref="A1:B413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17493,6 +17565,26 @@
       </c>
       <c r="B411" t="n">
         <v>0.24</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -17661,28 +17753,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6550618613503808</v>
+        <v>0.6546974705704613</v>
       </c>
       <c r="J2" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K2" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2206637569075109</v>
+        <v>0.2223357397580433</v>
       </c>
       <c r="M2" t="n">
-        <v>6.822123813813132</v>
+        <v>6.785968615900566</v>
       </c>
       <c r="N2" t="n">
-        <v>73.39035193321111</v>
+        <v>72.9835561279946</v>
       </c>
       <c r="O2" t="n">
-        <v>8.566816907884229</v>
+        <v>8.543041386297658</v>
       </c>
       <c r="P2" t="n">
-        <v>337.3660623503346</v>
+        <v>337.3705271993344</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17739,28 +17831,28 @@
         <v>0.1167</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6817450919251343</v>
+        <v>0.6829845990659434</v>
       </c>
       <c r="J3" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K3" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L3" t="n">
-        <v>0.30116352202771</v>
+        <v>0.3041831141335021</v>
       </c>
       <c r="M3" t="n">
-        <v>5.610946987535347</v>
+        <v>5.585399840908161</v>
       </c>
       <c r="N3" t="n">
-        <v>52.3095996876007</v>
+        <v>52.025075841345</v>
       </c>
       <c r="O3" t="n">
-        <v>7.232537569041774</v>
+        <v>7.212841038130883</v>
       </c>
       <c r="P3" t="n">
-        <v>338.5741092684518</v>
+        <v>338.5589393053393</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17817,28 +17909,28 @@
         <v>0.1314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.676415845861737</v>
+        <v>0.6776753682522371</v>
       </c>
       <c r="J4" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K4" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3155608886934853</v>
+        <v>0.3186776348314798</v>
       </c>
       <c r="M4" t="n">
-        <v>5.380647664112617</v>
+        <v>5.357700595330166</v>
       </c>
       <c r="N4" t="n">
-        <v>48.05733338802796</v>
+        <v>47.79751246263497</v>
       </c>
       <c r="O4" t="n">
-        <v>6.932339676330638</v>
+        <v>6.91357450691283</v>
       </c>
       <c r="P4" t="n">
-        <v>344.2294197186504</v>
+        <v>344.2140049403195</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17895,28 +17987,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6238276015506083</v>
+        <v>0.6246421017242926</v>
       </c>
       <c r="J5" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K5" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2894288161797336</v>
+        <v>0.2921855391668083</v>
       </c>
       <c r="M5" t="n">
-        <v>5.132216010173344</v>
+        <v>5.10820348026843</v>
       </c>
       <c r="N5" t="n">
-        <v>46.26744003183418</v>
+        <v>46.01337117016017</v>
       </c>
       <c r="O5" t="n">
-        <v>6.802017350156803</v>
+        <v>6.783315647245097</v>
       </c>
       <c r="P5" t="n">
-        <v>347.7608259522531</v>
+        <v>347.7508557625271</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17973,28 +18065,28 @@
         <v>0.0824</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6132913185051855</v>
+        <v>0.613687257647089</v>
       </c>
       <c r="J6" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K6" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2654120261912464</v>
+        <v>0.2677772458998527</v>
       </c>
       <c r="M6" t="n">
-        <v>5.399961240924638</v>
+        <v>5.372021494079941</v>
       </c>
       <c r="N6" t="n">
-        <v>50.41239442952487</v>
+        <v>50.13310412290902</v>
       </c>
       <c r="O6" t="n">
-        <v>7.100168619795228</v>
+        <v>7.080473439178275</v>
       </c>
       <c r="P6" t="n">
-        <v>346.6773510409131</v>
+        <v>346.6725068768593</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18051,28 +18143,28 @@
         <v>0.094</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6085464039338787</v>
+        <v>0.6084000941087225</v>
       </c>
       <c r="J7" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K7" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2666348032927591</v>
+        <v>0.2686610967335465</v>
       </c>
       <c r="M7" t="n">
-        <v>5.253065155644055</v>
+        <v>5.224599468192572</v>
       </c>
       <c r="N7" t="n">
-        <v>49.32548169634843</v>
+        <v>49.05161061518632</v>
       </c>
       <c r="O7" t="n">
-        <v>7.023210213025695</v>
+        <v>7.00368550230422</v>
       </c>
       <c r="P7" t="n">
-        <v>348.9818540113869</v>
+        <v>348.9836468933235</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18129,28 +18221,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6465242506856033</v>
+        <v>0.6434647524545221</v>
       </c>
       <c r="J8" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K8" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3013061587286172</v>
+        <v>0.3013983138939028</v>
       </c>
       <c r="M8" t="n">
-        <v>5.160453384099584</v>
+        <v>5.144964192017492</v>
       </c>
       <c r="N8" t="n">
-        <v>46.93847984833941</v>
+        <v>46.71960578671918</v>
       </c>
       <c r="O8" t="n">
-        <v>6.851166312996599</v>
+        <v>6.835174159209052</v>
       </c>
       <c r="P8" t="n">
-        <v>350.8464788054206</v>
+        <v>350.8839267840816</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18207,28 +18299,28 @@
         <v>0.0586</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4948947229071113</v>
+        <v>0.4903471947714495</v>
       </c>
       <c r="J9" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K9" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1672931784480782</v>
+        <v>0.1660111839950696</v>
       </c>
       <c r="M9" t="n">
-        <v>5.617282179551682</v>
+        <v>5.60741758252636</v>
       </c>
       <c r="N9" t="n">
-        <v>59.03641957051188</v>
+        <v>58.80186544605031</v>
       </c>
       <c r="O9" t="n">
-        <v>7.683516094244346</v>
+        <v>7.668237440641122</v>
       </c>
       <c r="P9" t="n">
-        <v>358.4410281015681</v>
+        <v>358.4966984661364</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18266,7 +18358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J359"/>
+  <dimension ref="A1:J361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36933,6 +37025,110 @@
         </is>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:14:11+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>-45.80001143796778,170.74147278304636</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>-45.80058673256875,170.74182197363947</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>-45.801139352019106,170.7422254279066</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-45.8016787851587,170.74261978419878</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-45.80220376509261,170.74307283270122</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-45.802723732422436,170.74356924884344</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-45.80323834430252,170.74405639882062</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-45.803719594605845,170.74461694417076</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>-45.80001277105244,170.74146731730468</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>-45.80058654644912,170.74182269812636</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>-45.80113990921041,170.74222353015128</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-45.80167836582526,170.74262092231643</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-45.80220464854398,170.74307074025734</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-45.80272458188329,170.74356727741457</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-45.803237691453766,170.74405778641076</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-45.803723795062105,170.74460858696253</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0504/nzd0504.xlsx
+++ b/data/nzd0504/nzd0504.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J361"/>
+  <dimension ref="A1:J363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13436,6 +13436,78 @@
         <v>367.27</v>
       </c>
       <c r="J361" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>354.69</v>
+      </c>
+      <c r="C362" t="n">
+        <v>358.09</v>
+      </c>
+      <c r="D362" t="n">
+        <v>363.53</v>
+      </c>
+      <c r="E362" t="n">
+        <v>365.09</v>
+      </c>
+      <c r="F362" t="n">
+        <v>363</v>
+      </c>
+      <c r="G362" t="n">
+        <v>364.78</v>
+      </c>
+      <c r="H362" t="n">
+        <v>365.18</v>
+      </c>
+      <c r="I362" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="C363" t="n">
+        <v>358.45</v>
+      </c>
+      <c r="D363" t="n">
+        <v>364.04</v>
+      </c>
+      <c r="E363" t="n">
+        <v>365.93</v>
+      </c>
+      <c r="F363" t="n">
+        <v>364.22</v>
+      </c>
+      <c r="G363" t="n">
+        <v>365.81</v>
+      </c>
+      <c r="H363" t="n">
+        <v>366.35</v>
+      </c>
+      <c r="I363" t="n">
+        <v>366.75</v>
+      </c>
+      <c r="J363" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13452,7 +13524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B413"/>
+  <dimension ref="A1:B415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17585,6 +17657,26 @@
       </c>
       <c r="B413" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -17753,28 +17845,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6546974705704613</v>
+        <v>0.6544298930108239</v>
       </c>
       <c r="J2" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K2" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2223357397580433</v>
+        <v>0.224062006997324</v>
       </c>
       <c r="M2" t="n">
-        <v>6.785968615900566</v>
+        <v>6.749745511645965</v>
       </c>
       <c r="N2" t="n">
-        <v>72.9835561279946</v>
+        <v>72.58073393254661</v>
       </c>
       <c r="O2" t="n">
-        <v>8.543041386297658</v>
+        <v>8.519432723635219</v>
       </c>
       <c r="P2" t="n">
-        <v>337.3705271993344</v>
+        <v>337.3738122402791</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17831,28 +17923,28 @@
         <v>0.1167</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6829845990659434</v>
+        <v>0.6843532251902609</v>
       </c>
       <c r="J3" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3041831141335021</v>
+        <v>0.3072824254568106</v>
       </c>
       <c r="M3" t="n">
-        <v>5.585399840908161</v>
+        <v>5.560670879922633</v>
       </c>
       <c r="N3" t="n">
-        <v>52.025075841345</v>
+        <v>51.74546446487241</v>
       </c>
       <c r="O3" t="n">
-        <v>7.212841038130883</v>
+        <v>7.193432036578396</v>
       </c>
       <c r="P3" t="n">
-        <v>338.5589393053393</v>
+        <v>338.5421242860265</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17909,28 +18001,28 @@
         <v>0.1314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6776753682522371</v>
+        <v>0.6790448566335999</v>
       </c>
       <c r="J4" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K4" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3186776348314798</v>
+        <v>0.3218631630505349</v>
       </c>
       <c r="M4" t="n">
-        <v>5.357700595330166</v>
+        <v>5.335548385488139</v>
       </c>
       <c r="N4" t="n">
-        <v>47.79751246263497</v>
+        <v>47.54220188040886</v>
       </c>
       <c r="O4" t="n">
-        <v>6.91357450691283</v>
+        <v>6.895085342503664</v>
       </c>
       <c r="P4" t="n">
-        <v>344.2140049403195</v>
+        <v>344.1971760551048</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17987,28 +18079,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6246421017242926</v>
+        <v>0.6255936495968266</v>
       </c>
       <c r="J5" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K5" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2921855391668083</v>
+        <v>0.2950302180760656</v>
       </c>
       <c r="M5" t="n">
-        <v>5.10820348026843</v>
+        <v>5.085157112977374</v>
       </c>
       <c r="N5" t="n">
-        <v>46.01337117016017</v>
+        <v>45.7641043198044</v>
       </c>
       <c r="O5" t="n">
-        <v>6.783315647245097</v>
+        <v>6.764917170210172</v>
       </c>
       <c r="P5" t="n">
-        <v>347.7508557625271</v>
+        <v>347.7391583398958</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18065,28 +18157,28 @@
         <v>0.0824</v>
       </c>
       <c r="I6" t="n">
-        <v>0.613687257647089</v>
+        <v>0.6140680992768</v>
       </c>
       <c r="J6" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K6" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2677772458998527</v>
+        <v>0.270130464187805</v>
       </c>
       <c r="M6" t="n">
-        <v>5.372021494079941</v>
+        <v>5.345678378721108</v>
       </c>
       <c r="N6" t="n">
-        <v>50.13310412290902</v>
+        <v>49.8587111073212</v>
       </c>
       <c r="O6" t="n">
-        <v>7.080473439178275</v>
+        <v>7.06107011063629</v>
       </c>
       <c r="P6" t="n">
-        <v>346.6725068768593</v>
+        <v>346.667817085205</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18143,28 +18235,28 @@
         <v>0.094</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6084000941087225</v>
+        <v>0.6082511583076711</v>
       </c>
       <c r="J7" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K7" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2686610967335465</v>
+        <v>0.2706817840452073</v>
       </c>
       <c r="M7" t="n">
-        <v>5.224599468192572</v>
+        <v>5.198459616050005</v>
       </c>
       <c r="N7" t="n">
-        <v>49.05161061518632</v>
+        <v>48.78206970790552</v>
       </c>
       <c r="O7" t="n">
-        <v>7.00368550230422</v>
+        <v>6.984416203800109</v>
       </c>
       <c r="P7" t="n">
-        <v>348.9836468933235</v>
+        <v>348.9854673384173</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18221,28 +18313,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6434647524545221</v>
+        <v>0.6407047718632506</v>
       </c>
       <c r="J8" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K8" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3013983138939028</v>
+        <v>0.3016938856418918</v>
       </c>
       <c r="M8" t="n">
-        <v>5.144964192017492</v>
+        <v>5.128255432520155</v>
       </c>
       <c r="N8" t="n">
-        <v>46.71960578671918</v>
+        <v>46.49770906459671</v>
       </c>
       <c r="O8" t="n">
-        <v>6.835174159209052</v>
+        <v>6.818922866890101</v>
       </c>
       <c r="P8" t="n">
-        <v>350.8839267840816</v>
+        <v>350.917823211004</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18299,28 +18391,28 @@
         <v>0.0586</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4903471947714495</v>
+        <v>0.4847093836421482</v>
       </c>
       <c r="J9" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K9" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1660111839950696</v>
+        <v>0.1639719853932814</v>
       </c>
       <c r="M9" t="n">
-        <v>5.60741758252636</v>
+        <v>5.602866879052727</v>
       </c>
       <c r="N9" t="n">
-        <v>58.80186544605031</v>
+        <v>58.62060991231469</v>
       </c>
       <c r="O9" t="n">
-        <v>7.668237440641122</v>
+        <v>7.656409727301347</v>
       </c>
       <c r="P9" t="n">
-        <v>358.4966984661364</v>
+        <v>358.5659581438323</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18358,7 +18450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J361"/>
+  <dimension ref="A1:J363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37129,6 +37221,110 @@
         </is>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>-45.80001211932219,170.74146998944508</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>-45.800586577469055,170.74182257737854</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>-45.80113987438595,170.74222364876098</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-45.80167949802551,170.74261784939873</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>-45.802206833923556,170.74306556421166</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-45.8027263751894,170.74356311550895</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-45.80323964999997,170.7440536236402</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-45.803727943012035,170.74460033421818</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>-45.800011289847255,170.74147339035096</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>-45.800585460751215,170.74182692429972</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>-45.801138098338555,170.74222969785595</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-45.801675975624505,170.74262740958667</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-45.80220116123567,170.74307899990387</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-45.80272151438564,170.743574396463</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-45.80323377436086,170.74406611195096</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-45.80372652535832,170.7446031547765</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
